--- a/data.mn/public/datasets/ebarilga-zip-zones.xlsx
+++ b/data.mn/public/datasets/ebarilga-zip-zones.xlsx
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Zamchin-BKhD</t>
+          <t>Zamchin-BKD</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -14233,7 +14233,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Khundlungiin am-SKhD</t>
+          <t>Khundlungiin am-SKD</t>
         </is>
       </c>
       <c r="C512" t="n">
